--- a/_rankGA_test.xlsx
+++ b/_rankGA_test.xlsx
@@ -8,11 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="genotype_histogram" localSheetId="0">Hoja1!$A$1:$D$257</definedName>
+    <definedName name="genotype_histogram" localSheetId="1">Hoja2!$A$1:$D$257</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,11 +36,21 @@
       </textFields>
     </textPr>
   </connection>
+  <connection id="2" name="genotype_histogram1" type="6" refreshedVersion="6" background="1" saveData="1">
+    <textPr codePage="850" sourceFile="C:\Users\usuario\Dropbox\NetBeansProjects\RankGA\genotype_histogram.csv" comma="1">
+      <textFields count="4">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="260">
   <si>
     <t>numOnes</t>
   </si>
@@ -886,7 +899,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Deceptive 1 block</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3312,25 +3349,15 @@
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
-              <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:multiLvlStrRef>
@@ -5840,6 +5867,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="156282848"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -5855,7 +5883,5071 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Deceptive 2 blocks</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
       <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja2!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Fitness</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Hoja2!$A$2:$B$257</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="256"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>'00000000'</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>'00000001'</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>'00000010'</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>'00000100'</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>'00001000'</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>'00010000'</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>'00100000'</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>'01000000'</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>'10000000'</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>'00010001'</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>'00010010'</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>'00010100'</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>'00011000'</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>'00100001'</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>'00100010'</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>'00100100'</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>'00101000'</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>'01000001'</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>'01000010'</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>'01000100'</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>'01001000'</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>'10000001'</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>'10000010'</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>'10000100'</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>'10001000'</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>'00000011'</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>'00000101'</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>'00000110'</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>'00001001'</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>'00001010'</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>'00001100'</c:v>
+                  </c:pt>
+                  <c:pt idx="31">
+                    <c:v>'00110000'</c:v>
+                  </c:pt>
+                  <c:pt idx="32">
+                    <c:v>'01010000'</c:v>
+                  </c:pt>
+                  <c:pt idx="33">
+                    <c:v>'01100000'</c:v>
+                  </c:pt>
+                  <c:pt idx="34">
+                    <c:v>'10010000'</c:v>
+                  </c:pt>
+                  <c:pt idx="35">
+                    <c:v>'10100000'</c:v>
+                  </c:pt>
+                  <c:pt idx="36">
+                    <c:v>'11000000'</c:v>
+                  </c:pt>
+                  <c:pt idx="37">
+                    <c:v>'00010011'</c:v>
+                  </c:pt>
+                  <c:pt idx="38">
+                    <c:v>'00010101'</c:v>
+                  </c:pt>
+                  <c:pt idx="39">
+                    <c:v>'00010110'</c:v>
+                  </c:pt>
+                  <c:pt idx="40">
+                    <c:v>'00011001'</c:v>
+                  </c:pt>
+                  <c:pt idx="41">
+                    <c:v>'00011010'</c:v>
+                  </c:pt>
+                  <c:pt idx="42">
+                    <c:v>'00011100'</c:v>
+                  </c:pt>
+                  <c:pt idx="43">
+                    <c:v>'00100011'</c:v>
+                  </c:pt>
+                  <c:pt idx="44">
+                    <c:v>'00100101'</c:v>
+                  </c:pt>
+                  <c:pt idx="45">
+                    <c:v>'00100110'</c:v>
+                  </c:pt>
+                  <c:pt idx="46">
+                    <c:v>'00101001'</c:v>
+                  </c:pt>
+                  <c:pt idx="47">
+                    <c:v>'00101010'</c:v>
+                  </c:pt>
+                  <c:pt idx="48">
+                    <c:v>'00101100'</c:v>
+                  </c:pt>
+                  <c:pt idx="49">
+                    <c:v>'00110001'</c:v>
+                  </c:pt>
+                  <c:pt idx="50">
+                    <c:v>'00110010'</c:v>
+                  </c:pt>
+                  <c:pt idx="51">
+                    <c:v>'00110100'</c:v>
+                  </c:pt>
+                  <c:pt idx="52">
+                    <c:v>'00111000'</c:v>
+                  </c:pt>
+                  <c:pt idx="53">
+                    <c:v>'01000011'</c:v>
+                  </c:pt>
+                  <c:pt idx="54">
+                    <c:v>'01000101'</c:v>
+                  </c:pt>
+                  <c:pt idx="55">
+                    <c:v>'01000110'</c:v>
+                  </c:pt>
+                  <c:pt idx="56">
+                    <c:v>'01001001'</c:v>
+                  </c:pt>
+                  <c:pt idx="57">
+                    <c:v>'01001010'</c:v>
+                  </c:pt>
+                  <c:pt idx="58">
+                    <c:v>'01001100'</c:v>
+                  </c:pt>
+                  <c:pt idx="59">
+                    <c:v>'01010001'</c:v>
+                  </c:pt>
+                  <c:pt idx="60">
+                    <c:v>'01010010'</c:v>
+                  </c:pt>
+                  <c:pt idx="61">
+                    <c:v>'01010100'</c:v>
+                  </c:pt>
+                  <c:pt idx="62">
+                    <c:v>'01011000'</c:v>
+                  </c:pt>
+                  <c:pt idx="63">
+                    <c:v>'01100001'</c:v>
+                  </c:pt>
+                  <c:pt idx="64">
+                    <c:v>'01100010'</c:v>
+                  </c:pt>
+                  <c:pt idx="65">
+                    <c:v>'01100100'</c:v>
+                  </c:pt>
+                  <c:pt idx="66">
+                    <c:v>'01101000'</c:v>
+                  </c:pt>
+                  <c:pt idx="67">
+                    <c:v>'10000011'</c:v>
+                  </c:pt>
+                  <c:pt idx="68">
+                    <c:v>'10000101'</c:v>
+                  </c:pt>
+                  <c:pt idx="69">
+                    <c:v>'10000110'</c:v>
+                  </c:pt>
+                  <c:pt idx="70">
+                    <c:v>'10001001'</c:v>
+                  </c:pt>
+                  <c:pt idx="71">
+                    <c:v>'10001010'</c:v>
+                  </c:pt>
+                  <c:pt idx="72">
+                    <c:v>'10001100'</c:v>
+                  </c:pt>
+                  <c:pt idx="73">
+                    <c:v>'10010001'</c:v>
+                  </c:pt>
+                  <c:pt idx="74">
+                    <c:v>'10010010'</c:v>
+                  </c:pt>
+                  <c:pt idx="75">
+                    <c:v>'10010100'</c:v>
+                  </c:pt>
+                  <c:pt idx="76">
+                    <c:v>'10011000'</c:v>
+                  </c:pt>
+                  <c:pt idx="77">
+                    <c:v>'10100001'</c:v>
+                  </c:pt>
+                  <c:pt idx="78">
+                    <c:v>'10100010'</c:v>
+                  </c:pt>
+                  <c:pt idx="79">
+                    <c:v>'10100100'</c:v>
+                  </c:pt>
+                  <c:pt idx="80">
+                    <c:v>'10101000'</c:v>
+                  </c:pt>
+                  <c:pt idx="81">
+                    <c:v>'11000001'</c:v>
+                  </c:pt>
+                  <c:pt idx="82">
+                    <c:v>'11000010'</c:v>
+                  </c:pt>
+                  <c:pt idx="83">
+                    <c:v>'11000100'</c:v>
+                  </c:pt>
+                  <c:pt idx="84">
+                    <c:v>'11001000'</c:v>
+                  </c:pt>
+                  <c:pt idx="85">
+                    <c:v>'00000111'</c:v>
+                  </c:pt>
+                  <c:pt idx="86">
+                    <c:v>'00001011'</c:v>
+                  </c:pt>
+                  <c:pt idx="87">
+                    <c:v>'00001101'</c:v>
+                  </c:pt>
+                  <c:pt idx="88">
+                    <c:v>'00001110'</c:v>
+                  </c:pt>
+                  <c:pt idx="89">
+                    <c:v>'01110000'</c:v>
+                  </c:pt>
+                  <c:pt idx="90">
+                    <c:v>'10110000'</c:v>
+                  </c:pt>
+                  <c:pt idx="91">
+                    <c:v>'11010000'</c:v>
+                  </c:pt>
+                  <c:pt idx="92">
+                    <c:v>'11100000'</c:v>
+                  </c:pt>
+                  <c:pt idx="93">
+                    <c:v>'00010111'</c:v>
+                  </c:pt>
+                  <c:pt idx="94">
+                    <c:v>'00011011'</c:v>
+                  </c:pt>
+                  <c:pt idx="95">
+                    <c:v>'00011101'</c:v>
+                  </c:pt>
+                  <c:pt idx="96">
+                    <c:v>'00011110'</c:v>
+                  </c:pt>
+                  <c:pt idx="97">
+                    <c:v>'00100111'</c:v>
+                  </c:pt>
+                  <c:pt idx="98">
+                    <c:v>'00101011'</c:v>
+                  </c:pt>
+                  <c:pt idx="99">
+                    <c:v>'00101101'</c:v>
+                  </c:pt>
+                  <c:pt idx="100">
+                    <c:v>'00101110'</c:v>
+                  </c:pt>
+                  <c:pt idx="101">
+                    <c:v>'00110011'</c:v>
+                  </c:pt>
+                  <c:pt idx="102">
+                    <c:v>'00110101'</c:v>
+                  </c:pt>
+                  <c:pt idx="103">
+                    <c:v>'00110110'</c:v>
+                  </c:pt>
+                  <c:pt idx="104">
+                    <c:v>'00111001'</c:v>
+                  </c:pt>
+                  <c:pt idx="105">
+                    <c:v>'00111010'</c:v>
+                  </c:pt>
+                  <c:pt idx="106">
+                    <c:v>'00111100'</c:v>
+                  </c:pt>
+                  <c:pt idx="107">
+                    <c:v>'01000111'</c:v>
+                  </c:pt>
+                  <c:pt idx="108">
+                    <c:v>'01001011'</c:v>
+                  </c:pt>
+                  <c:pt idx="109">
+                    <c:v>'01001101'</c:v>
+                  </c:pt>
+                  <c:pt idx="110">
+                    <c:v>'01001110'</c:v>
+                  </c:pt>
+                  <c:pt idx="111">
+                    <c:v>'01010011'</c:v>
+                  </c:pt>
+                  <c:pt idx="112">
+                    <c:v>'01010101'</c:v>
+                  </c:pt>
+                  <c:pt idx="113">
+                    <c:v>'01010110'</c:v>
+                  </c:pt>
+                  <c:pt idx="114">
+                    <c:v>'01011001'</c:v>
+                  </c:pt>
+                  <c:pt idx="115">
+                    <c:v>'01011010'</c:v>
+                  </c:pt>
+                  <c:pt idx="116">
+                    <c:v>'01011100'</c:v>
+                  </c:pt>
+                  <c:pt idx="117">
+                    <c:v>'01100011'</c:v>
+                  </c:pt>
+                  <c:pt idx="118">
+                    <c:v>'01100101'</c:v>
+                  </c:pt>
+                  <c:pt idx="119">
+                    <c:v>'01100110'</c:v>
+                  </c:pt>
+                  <c:pt idx="120">
+                    <c:v>'01101001'</c:v>
+                  </c:pt>
+                  <c:pt idx="121">
+                    <c:v>'01101010'</c:v>
+                  </c:pt>
+                  <c:pt idx="122">
+                    <c:v>'01101100'</c:v>
+                  </c:pt>
+                  <c:pt idx="123">
+                    <c:v>'01110001'</c:v>
+                  </c:pt>
+                  <c:pt idx="124">
+                    <c:v>'01110010'</c:v>
+                  </c:pt>
+                  <c:pt idx="125">
+                    <c:v>'01110100'</c:v>
+                  </c:pt>
+                  <c:pt idx="126">
+                    <c:v>'01111000'</c:v>
+                  </c:pt>
+                  <c:pt idx="127">
+                    <c:v>'10000111'</c:v>
+                  </c:pt>
+                  <c:pt idx="128">
+                    <c:v>'10001011'</c:v>
+                  </c:pt>
+                  <c:pt idx="129">
+                    <c:v>'10001101'</c:v>
+                  </c:pt>
+                  <c:pt idx="130">
+                    <c:v>'10001110'</c:v>
+                  </c:pt>
+                  <c:pt idx="131">
+                    <c:v>'10010011'</c:v>
+                  </c:pt>
+                  <c:pt idx="132">
+                    <c:v>'10010101'</c:v>
+                  </c:pt>
+                  <c:pt idx="133">
+                    <c:v>'10010110'</c:v>
+                  </c:pt>
+                  <c:pt idx="134">
+                    <c:v>'10011001'</c:v>
+                  </c:pt>
+                  <c:pt idx="135">
+                    <c:v>'10011010'</c:v>
+                  </c:pt>
+                  <c:pt idx="136">
+                    <c:v>'10011100'</c:v>
+                  </c:pt>
+                  <c:pt idx="137">
+                    <c:v>'10100011'</c:v>
+                  </c:pt>
+                  <c:pt idx="138">
+                    <c:v>'10100101'</c:v>
+                  </c:pt>
+                  <c:pt idx="139">
+                    <c:v>'10100110'</c:v>
+                  </c:pt>
+                  <c:pt idx="140">
+                    <c:v>'10101001'</c:v>
+                  </c:pt>
+                  <c:pt idx="141">
+                    <c:v>'10101010'</c:v>
+                  </c:pt>
+                  <c:pt idx="142">
+                    <c:v>'10101100'</c:v>
+                  </c:pt>
+                  <c:pt idx="143">
+                    <c:v>'10110001'</c:v>
+                  </c:pt>
+                  <c:pt idx="144">
+                    <c:v>'10110010'</c:v>
+                  </c:pt>
+                  <c:pt idx="145">
+                    <c:v>'10110100'</c:v>
+                  </c:pt>
+                  <c:pt idx="146">
+                    <c:v>'10111000'</c:v>
+                  </c:pt>
+                  <c:pt idx="147">
+                    <c:v>'11000011'</c:v>
+                  </c:pt>
+                  <c:pt idx="148">
+                    <c:v>'11000101'</c:v>
+                  </c:pt>
+                  <c:pt idx="149">
+                    <c:v>'11000110'</c:v>
+                  </c:pt>
+                  <c:pt idx="150">
+                    <c:v>'11001001'</c:v>
+                  </c:pt>
+                  <c:pt idx="151">
+                    <c:v>'11001010'</c:v>
+                  </c:pt>
+                  <c:pt idx="152">
+                    <c:v>'11001100'</c:v>
+                  </c:pt>
+                  <c:pt idx="153">
+                    <c:v>'11010001'</c:v>
+                  </c:pt>
+                  <c:pt idx="154">
+                    <c:v>'11010010'</c:v>
+                  </c:pt>
+                  <c:pt idx="155">
+                    <c:v>'11010100'</c:v>
+                  </c:pt>
+                  <c:pt idx="156">
+                    <c:v>'11011000'</c:v>
+                  </c:pt>
+                  <c:pt idx="157">
+                    <c:v>'11100001'</c:v>
+                  </c:pt>
+                  <c:pt idx="158">
+                    <c:v>'11100010'</c:v>
+                  </c:pt>
+                  <c:pt idx="159">
+                    <c:v>'11100100'</c:v>
+                  </c:pt>
+                  <c:pt idx="160">
+                    <c:v>'11101000'</c:v>
+                  </c:pt>
+                  <c:pt idx="161">
+                    <c:v>'00001111'</c:v>
+                  </c:pt>
+                  <c:pt idx="162">
+                    <c:v>'11110000'</c:v>
+                  </c:pt>
+                  <c:pt idx="163">
+                    <c:v>'00011111'</c:v>
+                  </c:pt>
+                  <c:pt idx="164">
+                    <c:v>'00101111'</c:v>
+                  </c:pt>
+                  <c:pt idx="165">
+                    <c:v>'00110111'</c:v>
+                  </c:pt>
+                  <c:pt idx="166">
+                    <c:v>'00111011'</c:v>
+                  </c:pt>
+                  <c:pt idx="167">
+                    <c:v>'00111101'</c:v>
+                  </c:pt>
+                  <c:pt idx="168">
+                    <c:v>'00111110'</c:v>
+                  </c:pt>
+                  <c:pt idx="169">
+                    <c:v>'01001111'</c:v>
+                  </c:pt>
+                  <c:pt idx="170">
+                    <c:v>'01010111'</c:v>
+                  </c:pt>
+                  <c:pt idx="171">
+                    <c:v>'01011011'</c:v>
+                  </c:pt>
+                  <c:pt idx="172">
+                    <c:v>'01011101'</c:v>
+                  </c:pt>
+                  <c:pt idx="173">
+                    <c:v>'01011110'</c:v>
+                  </c:pt>
+                  <c:pt idx="174">
+                    <c:v>'01100111'</c:v>
+                  </c:pt>
+                  <c:pt idx="175">
+                    <c:v>'01101011'</c:v>
+                  </c:pt>
+                  <c:pt idx="176">
+                    <c:v>'01101101'</c:v>
+                  </c:pt>
+                  <c:pt idx="177">
+                    <c:v>'01101110'</c:v>
+                  </c:pt>
+                  <c:pt idx="178">
+                    <c:v>'01110011'</c:v>
+                  </c:pt>
+                  <c:pt idx="179">
+                    <c:v>'01110101'</c:v>
+                  </c:pt>
+                  <c:pt idx="180">
+                    <c:v>'01110110'</c:v>
+                  </c:pt>
+                  <c:pt idx="181">
+                    <c:v>'01111001'</c:v>
+                  </c:pt>
+                  <c:pt idx="182">
+                    <c:v>'01111010'</c:v>
+                  </c:pt>
+                  <c:pt idx="183">
+                    <c:v>'01111100'</c:v>
+                  </c:pt>
+                  <c:pt idx="184">
+                    <c:v>'10001111'</c:v>
+                  </c:pt>
+                  <c:pt idx="185">
+                    <c:v>'10010111'</c:v>
+                  </c:pt>
+                  <c:pt idx="186">
+                    <c:v>'10011011'</c:v>
+                  </c:pt>
+                  <c:pt idx="187">
+                    <c:v>'10011101'</c:v>
+                  </c:pt>
+                  <c:pt idx="188">
+                    <c:v>'10011110'</c:v>
+                  </c:pt>
+                  <c:pt idx="189">
+                    <c:v>'10100111'</c:v>
+                  </c:pt>
+                  <c:pt idx="190">
+                    <c:v>'10101011'</c:v>
+                  </c:pt>
+                  <c:pt idx="191">
+                    <c:v>'10101101'</c:v>
+                  </c:pt>
+                  <c:pt idx="192">
+                    <c:v>'10101110'</c:v>
+                  </c:pt>
+                  <c:pt idx="193">
+                    <c:v>'10110011'</c:v>
+                  </c:pt>
+                  <c:pt idx="194">
+                    <c:v>'10110101'</c:v>
+                  </c:pt>
+                  <c:pt idx="195">
+                    <c:v>'10110110'</c:v>
+                  </c:pt>
+                  <c:pt idx="196">
+                    <c:v>'10111001'</c:v>
+                  </c:pt>
+                  <c:pt idx="197">
+                    <c:v>'10111010'</c:v>
+                  </c:pt>
+                  <c:pt idx="198">
+                    <c:v>'10111100'</c:v>
+                  </c:pt>
+                  <c:pt idx="199">
+                    <c:v>'11000111'</c:v>
+                  </c:pt>
+                  <c:pt idx="200">
+                    <c:v>'11001011'</c:v>
+                  </c:pt>
+                  <c:pt idx="201">
+                    <c:v>'11001101'</c:v>
+                  </c:pt>
+                  <c:pt idx="202">
+                    <c:v>'11001110'</c:v>
+                  </c:pt>
+                  <c:pt idx="203">
+                    <c:v>'11010011'</c:v>
+                  </c:pt>
+                  <c:pt idx="204">
+                    <c:v>'11010101'</c:v>
+                  </c:pt>
+                  <c:pt idx="205">
+                    <c:v>'11010110'</c:v>
+                  </c:pt>
+                  <c:pt idx="206">
+                    <c:v>'11011001'</c:v>
+                  </c:pt>
+                  <c:pt idx="207">
+                    <c:v>'11011010'</c:v>
+                  </c:pt>
+                  <c:pt idx="208">
+                    <c:v>'11011100'</c:v>
+                  </c:pt>
+                  <c:pt idx="209">
+                    <c:v>'11100011'</c:v>
+                  </c:pt>
+                  <c:pt idx="210">
+                    <c:v>'11100101'</c:v>
+                  </c:pt>
+                  <c:pt idx="211">
+                    <c:v>'11100110'</c:v>
+                  </c:pt>
+                  <c:pt idx="212">
+                    <c:v>'11101001'</c:v>
+                  </c:pt>
+                  <c:pt idx="213">
+                    <c:v>'11101010'</c:v>
+                  </c:pt>
+                  <c:pt idx="214">
+                    <c:v>'11101100'</c:v>
+                  </c:pt>
+                  <c:pt idx="215">
+                    <c:v>'11110001'</c:v>
+                  </c:pt>
+                  <c:pt idx="216">
+                    <c:v>'11110010'</c:v>
+                  </c:pt>
+                  <c:pt idx="217">
+                    <c:v>'11110100'</c:v>
+                  </c:pt>
+                  <c:pt idx="218">
+                    <c:v>'11111000'</c:v>
+                  </c:pt>
+                  <c:pt idx="219">
+                    <c:v>'00111111'</c:v>
+                  </c:pt>
+                  <c:pt idx="220">
+                    <c:v>'01011111'</c:v>
+                  </c:pt>
+                  <c:pt idx="221">
+                    <c:v>'01101111'</c:v>
+                  </c:pt>
+                  <c:pt idx="222">
+                    <c:v>'01110111'</c:v>
+                  </c:pt>
+                  <c:pt idx="223">
+                    <c:v>'01111011'</c:v>
+                  </c:pt>
+                  <c:pt idx="224">
+                    <c:v>'01111101'</c:v>
+                  </c:pt>
+                  <c:pt idx="225">
+                    <c:v>'01111110'</c:v>
+                  </c:pt>
+                  <c:pt idx="226">
+                    <c:v>'10011111'</c:v>
+                  </c:pt>
+                  <c:pt idx="227">
+                    <c:v>'10101111'</c:v>
+                  </c:pt>
+                  <c:pt idx="228">
+                    <c:v>'10110111'</c:v>
+                  </c:pt>
+                  <c:pt idx="229">
+                    <c:v>'10111011'</c:v>
+                  </c:pt>
+                  <c:pt idx="230">
+                    <c:v>'10111101'</c:v>
+                  </c:pt>
+                  <c:pt idx="231">
+                    <c:v>'10111110'</c:v>
+                  </c:pt>
+                  <c:pt idx="232">
+                    <c:v>'11001111'</c:v>
+                  </c:pt>
+                  <c:pt idx="233">
+                    <c:v>'11010111'</c:v>
+                  </c:pt>
+                  <c:pt idx="234">
+                    <c:v>'11011011'</c:v>
+                  </c:pt>
+                  <c:pt idx="235">
+                    <c:v>'11011101'</c:v>
+                  </c:pt>
+                  <c:pt idx="236">
+                    <c:v>'11011110'</c:v>
+                  </c:pt>
+                  <c:pt idx="237">
+                    <c:v>'11100111'</c:v>
+                  </c:pt>
+                  <c:pt idx="238">
+                    <c:v>'11101011'</c:v>
+                  </c:pt>
+                  <c:pt idx="239">
+                    <c:v>'11101101'</c:v>
+                  </c:pt>
+                  <c:pt idx="240">
+                    <c:v>'11101110'</c:v>
+                  </c:pt>
+                  <c:pt idx="241">
+                    <c:v>'11110011'</c:v>
+                  </c:pt>
+                  <c:pt idx="242">
+                    <c:v>'11110101'</c:v>
+                  </c:pt>
+                  <c:pt idx="243">
+                    <c:v>'11110110'</c:v>
+                  </c:pt>
+                  <c:pt idx="244">
+                    <c:v>'11111001'</c:v>
+                  </c:pt>
+                  <c:pt idx="245">
+                    <c:v>'11111010'</c:v>
+                  </c:pt>
+                  <c:pt idx="246">
+                    <c:v>'11111100'</c:v>
+                  </c:pt>
+                  <c:pt idx="247">
+                    <c:v>'01111111'</c:v>
+                  </c:pt>
+                  <c:pt idx="248">
+                    <c:v>'10111111'</c:v>
+                  </c:pt>
+                  <c:pt idx="249">
+                    <c:v>'11011111'</c:v>
+                  </c:pt>
+                  <c:pt idx="250">
+                    <c:v>'11101111'</c:v>
+                  </c:pt>
+                  <c:pt idx="251">
+                    <c:v>'11110111'</c:v>
+                  </c:pt>
+                  <c:pt idx="252">
+                    <c:v>'11111011'</c:v>
+                  </c:pt>
+                  <c:pt idx="253">
+                    <c:v>'11111101'</c:v>
+                  </c:pt>
+                  <c:pt idx="254">
+                    <c:v>'11111110'</c:v>
+                  </c:pt>
+                  <c:pt idx="255">
+                    <c:v>'11111111'</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="31">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="32">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="33">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="34">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="35">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="36">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="37">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="38">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="39">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="40">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="41">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="42">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="43">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="44">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="45">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="46">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="47">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="48">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="49">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="50">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="51">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="52">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="53">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="54">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="55">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="56">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="57">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="58">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="59">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="60">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="61">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="62">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="63">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="64">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="65">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="66">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="67">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="68">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="69">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="70">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="71">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="72">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="73">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="74">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="75">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="76">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="77">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="78">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="79">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="80">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="81">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="82">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="83">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="84">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="85">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="86">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="87">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="88">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="89">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="90">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="91">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="92">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="93">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="94">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="95">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="96">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="97">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="98">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="99">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="100">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="101">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="102">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="103">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="104">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="105">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="106">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="107">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="108">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="109">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="110">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="111">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="112">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="113">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="114">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="115">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="116">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="117">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="118">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="119">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="120">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="121">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="122">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="123">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="124">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="125">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="126">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="127">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="128">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="129">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="130">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="131">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="132">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="133">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="134">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="135">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="136">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="137">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="138">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="139">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="140">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="141">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="142">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="143">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="144">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="145">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="146">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="147">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="148">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="149">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="150">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="151">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="152">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="153">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="154">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="155">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="156">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="157">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="158">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="159">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="160">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="161">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="162">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="163">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="164">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="165">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="166">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="167">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="168">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="169">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="170">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="171">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="172">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="173">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="174">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="175">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="176">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="177">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="178">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="179">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="180">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="181">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="182">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="183">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="184">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="185">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="186">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="187">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="188">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="189">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="190">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="191">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="192">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="193">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="194">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="195">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="196">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="197">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="198">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="199">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="200">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="201">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="202">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="203">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="204">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="205">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="206">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="207">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="208">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="209">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="210">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="211">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="212">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="213">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="214">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="215">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="216">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="217">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="218">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="219">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="220">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="221">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="222">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="223">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="224">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="225">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="226">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="227">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="228">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="229">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="230">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="231">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="232">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="233">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="234">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="235">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="236">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="237">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="238">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="239">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="240">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="241">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="242">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="243">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="244">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="245">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="246">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="247">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="248">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="249">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="250">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="251">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="252">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="253">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="254">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="255">
+                    <c:v>8</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja2!$D$2:$D$257</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="256"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-74BA-4934-9368-AE4F02A83594}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="356841632"/>
+        <c:axId val="356845896"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja2!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tests</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Hoja2!$A$2:$B$257</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="256"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>'00000000'</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>'00000001'</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>'00000010'</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>'00000100'</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>'00001000'</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>'00010000'</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>'00100000'</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>'01000000'</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>'10000000'</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>'00010001'</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>'00010010'</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>'00010100'</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>'00011000'</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>'00100001'</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>'00100010'</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>'00100100'</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>'00101000'</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>'01000001'</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>'01000010'</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>'01000100'</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>'01001000'</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>'10000001'</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>'10000010'</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>'10000100'</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>'10001000'</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>'00000011'</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>'00000101'</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>'00000110'</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>'00001001'</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>'00001010'</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>'00001100'</c:v>
+                  </c:pt>
+                  <c:pt idx="31">
+                    <c:v>'00110000'</c:v>
+                  </c:pt>
+                  <c:pt idx="32">
+                    <c:v>'01010000'</c:v>
+                  </c:pt>
+                  <c:pt idx="33">
+                    <c:v>'01100000'</c:v>
+                  </c:pt>
+                  <c:pt idx="34">
+                    <c:v>'10010000'</c:v>
+                  </c:pt>
+                  <c:pt idx="35">
+                    <c:v>'10100000'</c:v>
+                  </c:pt>
+                  <c:pt idx="36">
+                    <c:v>'11000000'</c:v>
+                  </c:pt>
+                  <c:pt idx="37">
+                    <c:v>'00010011'</c:v>
+                  </c:pt>
+                  <c:pt idx="38">
+                    <c:v>'00010101'</c:v>
+                  </c:pt>
+                  <c:pt idx="39">
+                    <c:v>'00010110'</c:v>
+                  </c:pt>
+                  <c:pt idx="40">
+                    <c:v>'00011001'</c:v>
+                  </c:pt>
+                  <c:pt idx="41">
+                    <c:v>'00011010'</c:v>
+                  </c:pt>
+                  <c:pt idx="42">
+                    <c:v>'00011100'</c:v>
+                  </c:pt>
+                  <c:pt idx="43">
+                    <c:v>'00100011'</c:v>
+                  </c:pt>
+                  <c:pt idx="44">
+                    <c:v>'00100101'</c:v>
+                  </c:pt>
+                  <c:pt idx="45">
+                    <c:v>'00100110'</c:v>
+                  </c:pt>
+                  <c:pt idx="46">
+                    <c:v>'00101001'</c:v>
+                  </c:pt>
+                  <c:pt idx="47">
+                    <c:v>'00101010'</c:v>
+                  </c:pt>
+                  <c:pt idx="48">
+                    <c:v>'00101100'</c:v>
+                  </c:pt>
+                  <c:pt idx="49">
+                    <c:v>'00110001'</c:v>
+                  </c:pt>
+                  <c:pt idx="50">
+                    <c:v>'00110010'</c:v>
+                  </c:pt>
+                  <c:pt idx="51">
+                    <c:v>'00110100'</c:v>
+                  </c:pt>
+                  <c:pt idx="52">
+                    <c:v>'00111000'</c:v>
+                  </c:pt>
+                  <c:pt idx="53">
+                    <c:v>'01000011'</c:v>
+                  </c:pt>
+                  <c:pt idx="54">
+                    <c:v>'01000101'</c:v>
+                  </c:pt>
+                  <c:pt idx="55">
+                    <c:v>'01000110'</c:v>
+                  </c:pt>
+                  <c:pt idx="56">
+                    <c:v>'01001001'</c:v>
+                  </c:pt>
+                  <c:pt idx="57">
+                    <c:v>'01001010'</c:v>
+                  </c:pt>
+                  <c:pt idx="58">
+                    <c:v>'01001100'</c:v>
+                  </c:pt>
+                  <c:pt idx="59">
+                    <c:v>'01010001'</c:v>
+                  </c:pt>
+                  <c:pt idx="60">
+                    <c:v>'01010010'</c:v>
+                  </c:pt>
+                  <c:pt idx="61">
+                    <c:v>'01010100'</c:v>
+                  </c:pt>
+                  <c:pt idx="62">
+                    <c:v>'01011000'</c:v>
+                  </c:pt>
+                  <c:pt idx="63">
+                    <c:v>'01100001'</c:v>
+                  </c:pt>
+                  <c:pt idx="64">
+                    <c:v>'01100010'</c:v>
+                  </c:pt>
+                  <c:pt idx="65">
+                    <c:v>'01100100'</c:v>
+                  </c:pt>
+                  <c:pt idx="66">
+                    <c:v>'01101000'</c:v>
+                  </c:pt>
+                  <c:pt idx="67">
+                    <c:v>'10000011'</c:v>
+                  </c:pt>
+                  <c:pt idx="68">
+                    <c:v>'10000101'</c:v>
+                  </c:pt>
+                  <c:pt idx="69">
+                    <c:v>'10000110'</c:v>
+                  </c:pt>
+                  <c:pt idx="70">
+                    <c:v>'10001001'</c:v>
+                  </c:pt>
+                  <c:pt idx="71">
+                    <c:v>'10001010'</c:v>
+                  </c:pt>
+                  <c:pt idx="72">
+                    <c:v>'10001100'</c:v>
+                  </c:pt>
+                  <c:pt idx="73">
+                    <c:v>'10010001'</c:v>
+                  </c:pt>
+                  <c:pt idx="74">
+                    <c:v>'10010010'</c:v>
+                  </c:pt>
+                  <c:pt idx="75">
+                    <c:v>'10010100'</c:v>
+                  </c:pt>
+                  <c:pt idx="76">
+                    <c:v>'10011000'</c:v>
+                  </c:pt>
+                  <c:pt idx="77">
+                    <c:v>'10100001'</c:v>
+                  </c:pt>
+                  <c:pt idx="78">
+                    <c:v>'10100010'</c:v>
+                  </c:pt>
+                  <c:pt idx="79">
+                    <c:v>'10100100'</c:v>
+                  </c:pt>
+                  <c:pt idx="80">
+                    <c:v>'10101000'</c:v>
+                  </c:pt>
+                  <c:pt idx="81">
+                    <c:v>'11000001'</c:v>
+                  </c:pt>
+                  <c:pt idx="82">
+                    <c:v>'11000010'</c:v>
+                  </c:pt>
+                  <c:pt idx="83">
+                    <c:v>'11000100'</c:v>
+                  </c:pt>
+                  <c:pt idx="84">
+                    <c:v>'11001000'</c:v>
+                  </c:pt>
+                  <c:pt idx="85">
+                    <c:v>'00000111'</c:v>
+                  </c:pt>
+                  <c:pt idx="86">
+                    <c:v>'00001011'</c:v>
+                  </c:pt>
+                  <c:pt idx="87">
+                    <c:v>'00001101'</c:v>
+                  </c:pt>
+                  <c:pt idx="88">
+                    <c:v>'00001110'</c:v>
+                  </c:pt>
+                  <c:pt idx="89">
+                    <c:v>'01110000'</c:v>
+                  </c:pt>
+                  <c:pt idx="90">
+                    <c:v>'10110000'</c:v>
+                  </c:pt>
+                  <c:pt idx="91">
+                    <c:v>'11010000'</c:v>
+                  </c:pt>
+                  <c:pt idx="92">
+                    <c:v>'11100000'</c:v>
+                  </c:pt>
+                  <c:pt idx="93">
+                    <c:v>'00010111'</c:v>
+                  </c:pt>
+                  <c:pt idx="94">
+                    <c:v>'00011011'</c:v>
+                  </c:pt>
+                  <c:pt idx="95">
+                    <c:v>'00011101'</c:v>
+                  </c:pt>
+                  <c:pt idx="96">
+                    <c:v>'00011110'</c:v>
+                  </c:pt>
+                  <c:pt idx="97">
+                    <c:v>'00100111'</c:v>
+                  </c:pt>
+                  <c:pt idx="98">
+                    <c:v>'00101011'</c:v>
+                  </c:pt>
+                  <c:pt idx="99">
+                    <c:v>'00101101'</c:v>
+                  </c:pt>
+                  <c:pt idx="100">
+                    <c:v>'00101110'</c:v>
+                  </c:pt>
+                  <c:pt idx="101">
+                    <c:v>'00110011'</c:v>
+                  </c:pt>
+                  <c:pt idx="102">
+                    <c:v>'00110101'</c:v>
+                  </c:pt>
+                  <c:pt idx="103">
+                    <c:v>'00110110'</c:v>
+                  </c:pt>
+                  <c:pt idx="104">
+                    <c:v>'00111001'</c:v>
+                  </c:pt>
+                  <c:pt idx="105">
+                    <c:v>'00111010'</c:v>
+                  </c:pt>
+                  <c:pt idx="106">
+                    <c:v>'00111100'</c:v>
+                  </c:pt>
+                  <c:pt idx="107">
+                    <c:v>'01000111'</c:v>
+                  </c:pt>
+                  <c:pt idx="108">
+                    <c:v>'01001011'</c:v>
+                  </c:pt>
+                  <c:pt idx="109">
+                    <c:v>'01001101'</c:v>
+                  </c:pt>
+                  <c:pt idx="110">
+                    <c:v>'01001110'</c:v>
+                  </c:pt>
+                  <c:pt idx="111">
+                    <c:v>'01010011'</c:v>
+                  </c:pt>
+                  <c:pt idx="112">
+                    <c:v>'01010101'</c:v>
+                  </c:pt>
+                  <c:pt idx="113">
+                    <c:v>'01010110'</c:v>
+                  </c:pt>
+                  <c:pt idx="114">
+                    <c:v>'01011001'</c:v>
+                  </c:pt>
+                  <c:pt idx="115">
+                    <c:v>'01011010'</c:v>
+                  </c:pt>
+                  <c:pt idx="116">
+                    <c:v>'01011100'</c:v>
+                  </c:pt>
+                  <c:pt idx="117">
+                    <c:v>'01100011'</c:v>
+                  </c:pt>
+                  <c:pt idx="118">
+                    <c:v>'01100101'</c:v>
+                  </c:pt>
+                  <c:pt idx="119">
+                    <c:v>'01100110'</c:v>
+                  </c:pt>
+                  <c:pt idx="120">
+                    <c:v>'01101001'</c:v>
+                  </c:pt>
+                  <c:pt idx="121">
+                    <c:v>'01101010'</c:v>
+                  </c:pt>
+                  <c:pt idx="122">
+                    <c:v>'01101100'</c:v>
+                  </c:pt>
+                  <c:pt idx="123">
+                    <c:v>'01110001'</c:v>
+                  </c:pt>
+                  <c:pt idx="124">
+                    <c:v>'01110010'</c:v>
+                  </c:pt>
+                  <c:pt idx="125">
+                    <c:v>'01110100'</c:v>
+                  </c:pt>
+                  <c:pt idx="126">
+                    <c:v>'01111000'</c:v>
+                  </c:pt>
+                  <c:pt idx="127">
+                    <c:v>'10000111'</c:v>
+                  </c:pt>
+                  <c:pt idx="128">
+                    <c:v>'10001011'</c:v>
+                  </c:pt>
+                  <c:pt idx="129">
+                    <c:v>'10001101'</c:v>
+                  </c:pt>
+                  <c:pt idx="130">
+                    <c:v>'10001110'</c:v>
+                  </c:pt>
+                  <c:pt idx="131">
+                    <c:v>'10010011'</c:v>
+                  </c:pt>
+                  <c:pt idx="132">
+                    <c:v>'10010101'</c:v>
+                  </c:pt>
+                  <c:pt idx="133">
+                    <c:v>'10010110'</c:v>
+                  </c:pt>
+                  <c:pt idx="134">
+                    <c:v>'10011001'</c:v>
+                  </c:pt>
+                  <c:pt idx="135">
+                    <c:v>'10011010'</c:v>
+                  </c:pt>
+                  <c:pt idx="136">
+                    <c:v>'10011100'</c:v>
+                  </c:pt>
+                  <c:pt idx="137">
+                    <c:v>'10100011'</c:v>
+                  </c:pt>
+                  <c:pt idx="138">
+                    <c:v>'10100101'</c:v>
+                  </c:pt>
+                  <c:pt idx="139">
+                    <c:v>'10100110'</c:v>
+                  </c:pt>
+                  <c:pt idx="140">
+                    <c:v>'10101001'</c:v>
+                  </c:pt>
+                  <c:pt idx="141">
+                    <c:v>'10101010'</c:v>
+                  </c:pt>
+                  <c:pt idx="142">
+                    <c:v>'10101100'</c:v>
+                  </c:pt>
+                  <c:pt idx="143">
+                    <c:v>'10110001'</c:v>
+                  </c:pt>
+                  <c:pt idx="144">
+                    <c:v>'10110010'</c:v>
+                  </c:pt>
+                  <c:pt idx="145">
+                    <c:v>'10110100'</c:v>
+                  </c:pt>
+                  <c:pt idx="146">
+                    <c:v>'10111000'</c:v>
+                  </c:pt>
+                  <c:pt idx="147">
+                    <c:v>'11000011'</c:v>
+                  </c:pt>
+                  <c:pt idx="148">
+                    <c:v>'11000101'</c:v>
+                  </c:pt>
+                  <c:pt idx="149">
+                    <c:v>'11000110'</c:v>
+                  </c:pt>
+                  <c:pt idx="150">
+                    <c:v>'11001001'</c:v>
+                  </c:pt>
+                  <c:pt idx="151">
+                    <c:v>'11001010'</c:v>
+                  </c:pt>
+                  <c:pt idx="152">
+                    <c:v>'11001100'</c:v>
+                  </c:pt>
+                  <c:pt idx="153">
+                    <c:v>'11010001'</c:v>
+                  </c:pt>
+                  <c:pt idx="154">
+                    <c:v>'11010010'</c:v>
+                  </c:pt>
+                  <c:pt idx="155">
+                    <c:v>'11010100'</c:v>
+                  </c:pt>
+                  <c:pt idx="156">
+                    <c:v>'11011000'</c:v>
+                  </c:pt>
+                  <c:pt idx="157">
+                    <c:v>'11100001'</c:v>
+                  </c:pt>
+                  <c:pt idx="158">
+                    <c:v>'11100010'</c:v>
+                  </c:pt>
+                  <c:pt idx="159">
+                    <c:v>'11100100'</c:v>
+                  </c:pt>
+                  <c:pt idx="160">
+                    <c:v>'11101000'</c:v>
+                  </c:pt>
+                  <c:pt idx="161">
+                    <c:v>'00001111'</c:v>
+                  </c:pt>
+                  <c:pt idx="162">
+                    <c:v>'11110000'</c:v>
+                  </c:pt>
+                  <c:pt idx="163">
+                    <c:v>'00011111'</c:v>
+                  </c:pt>
+                  <c:pt idx="164">
+                    <c:v>'00101111'</c:v>
+                  </c:pt>
+                  <c:pt idx="165">
+                    <c:v>'00110111'</c:v>
+                  </c:pt>
+                  <c:pt idx="166">
+                    <c:v>'00111011'</c:v>
+                  </c:pt>
+                  <c:pt idx="167">
+                    <c:v>'00111101'</c:v>
+                  </c:pt>
+                  <c:pt idx="168">
+                    <c:v>'00111110'</c:v>
+                  </c:pt>
+                  <c:pt idx="169">
+                    <c:v>'01001111'</c:v>
+                  </c:pt>
+                  <c:pt idx="170">
+                    <c:v>'01010111'</c:v>
+                  </c:pt>
+                  <c:pt idx="171">
+                    <c:v>'01011011'</c:v>
+                  </c:pt>
+                  <c:pt idx="172">
+                    <c:v>'01011101'</c:v>
+                  </c:pt>
+                  <c:pt idx="173">
+                    <c:v>'01011110'</c:v>
+                  </c:pt>
+                  <c:pt idx="174">
+                    <c:v>'01100111'</c:v>
+                  </c:pt>
+                  <c:pt idx="175">
+                    <c:v>'01101011'</c:v>
+                  </c:pt>
+                  <c:pt idx="176">
+                    <c:v>'01101101'</c:v>
+                  </c:pt>
+                  <c:pt idx="177">
+                    <c:v>'01101110'</c:v>
+                  </c:pt>
+                  <c:pt idx="178">
+                    <c:v>'01110011'</c:v>
+                  </c:pt>
+                  <c:pt idx="179">
+                    <c:v>'01110101'</c:v>
+                  </c:pt>
+                  <c:pt idx="180">
+                    <c:v>'01110110'</c:v>
+                  </c:pt>
+                  <c:pt idx="181">
+                    <c:v>'01111001'</c:v>
+                  </c:pt>
+                  <c:pt idx="182">
+                    <c:v>'01111010'</c:v>
+                  </c:pt>
+                  <c:pt idx="183">
+                    <c:v>'01111100'</c:v>
+                  </c:pt>
+                  <c:pt idx="184">
+                    <c:v>'10001111'</c:v>
+                  </c:pt>
+                  <c:pt idx="185">
+                    <c:v>'10010111'</c:v>
+                  </c:pt>
+                  <c:pt idx="186">
+                    <c:v>'10011011'</c:v>
+                  </c:pt>
+                  <c:pt idx="187">
+                    <c:v>'10011101'</c:v>
+                  </c:pt>
+                  <c:pt idx="188">
+                    <c:v>'10011110'</c:v>
+                  </c:pt>
+                  <c:pt idx="189">
+                    <c:v>'10100111'</c:v>
+                  </c:pt>
+                  <c:pt idx="190">
+                    <c:v>'10101011'</c:v>
+                  </c:pt>
+                  <c:pt idx="191">
+                    <c:v>'10101101'</c:v>
+                  </c:pt>
+                  <c:pt idx="192">
+                    <c:v>'10101110'</c:v>
+                  </c:pt>
+                  <c:pt idx="193">
+                    <c:v>'10110011'</c:v>
+                  </c:pt>
+                  <c:pt idx="194">
+                    <c:v>'10110101'</c:v>
+                  </c:pt>
+                  <c:pt idx="195">
+                    <c:v>'10110110'</c:v>
+                  </c:pt>
+                  <c:pt idx="196">
+                    <c:v>'10111001'</c:v>
+                  </c:pt>
+                  <c:pt idx="197">
+                    <c:v>'10111010'</c:v>
+                  </c:pt>
+                  <c:pt idx="198">
+                    <c:v>'10111100'</c:v>
+                  </c:pt>
+                  <c:pt idx="199">
+                    <c:v>'11000111'</c:v>
+                  </c:pt>
+                  <c:pt idx="200">
+                    <c:v>'11001011'</c:v>
+                  </c:pt>
+                  <c:pt idx="201">
+                    <c:v>'11001101'</c:v>
+                  </c:pt>
+                  <c:pt idx="202">
+                    <c:v>'11001110'</c:v>
+                  </c:pt>
+                  <c:pt idx="203">
+                    <c:v>'11010011'</c:v>
+                  </c:pt>
+                  <c:pt idx="204">
+                    <c:v>'11010101'</c:v>
+                  </c:pt>
+                  <c:pt idx="205">
+                    <c:v>'11010110'</c:v>
+                  </c:pt>
+                  <c:pt idx="206">
+                    <c:v>'11011001'</c:v>
+                  </c:pt>
+                  <c:pt idx="207">
+                    <c:v>'11011010'</c:v>
+                  </c:pt>
+                  <c:pt idx="208">
+                    <c:v>'11011100'</c:v>
+                  </c:pt>
+                  <c:pt idx="209">
+                    <c:v>'11100011'</c:v>
+                  </c:pt>
+                  <c:pt idx="210">
+                    <c:v>'11100101'</c:v>
+                  </c:pt>
+                  <c:pt idx="211">
+                    <c:v>'11100110'</c:v>
+                  </c:pt>
+                  <c:pt idx="212">
+                    <c:v>'11101001'</c:v>
+                  </c:pt>
+                  <c:pt idx="213">
+                    <c:v>'11101010'</c:v>
+                  </c:pt>
+                  <c:pt idx="214">
+                    <c:v>'11101100'</c:v>
+                  </c:pt>
+                  <c:pt idx="215">
+                    <c:v>'11110001'</c:v>
+                  </c:pt>
+                  <c:pt idx="216">
+                    <c:v>'11110010'</c:v>
+                  </c:pt>
+                  <c:pt idx="217">
+                    <c:v>'11110100'</c:v>
+                  </c:pt>
+                  <c:pt idx="218">
+                    <c:v>'11111000'</c:v>
+                  </c:pt>
+                  <c:pt idx="219">
+                    <c:v>'00111111'</c:v>
+                  </c:pt>
+                  <c:pt idx="220">
+                    <c:v>'01011111'</c:v>
+                  </c:pt>
+                  <c:pt idx="221">
+                    <c:v>'01101111'</c:v>
+                  </c:pt>
+                  <c:pt idx="222">
+                    <c:v>'01110111'</c:v>
+                  </c:pt>
+                  <c:pt idx="223">
+                    <c:v>'01111011'</c:v>
+                  </c:pt>
+                  <c:pt idx="224">
+                    <c:v>'01111101'</c:v>
+                  </c:pt>
+                  <c:pt idx="225">
+                    <c:v>'01111110'</c:v>
+                  </c:pt>
+                  <c:pt idx="226">
+                    <c:v>'10011111'</c:v>
+                  </c:pt>
+                  <c:pt idx="227">
+                    <c:v>'10101111'</c:v>
+                  </c:pt>
+                  <c:pt idx="228">
+                    <c:v>'10110111'</c:v>
+                  </c:pt>
+                  <c:pt idx="229">
+                    <c:v>'10111011'</c:v>
+                  </c:pt>
+                  <c:pt idx="230">
+                    <c:v>'10111101'</c:v>
+                  </c:pt>
+                  <c:pt idx="231">
+                    <c:v>'10111110'</c:v>
+                  </c:pt>
+                  <c:pt idx="232">
+                    <c:v>'11001111'</c:v>
+                  </c:pt>
+                  <c:pt idx="233">
+                    <c:v>'11010111'</c:v>
+                  </c:pt>
+                  <c:pt idx="234">
+                    <c:v>'11011011'</c:v>
+                  </c:pt>
+                  <c:pt idx="235">
+                    <c:v>'11011101'</c:v>
+                  </c:pt>
+                  <c:pt idx="236">
+                    <c:v>'11011110'</c:v>
+                  </c:pt>
+                  <c:pt idx="237">
+                    <c:v>'11100111'</c:v>
+                  </c:pt>
+                  <c:pt idx="238">
+                    <c:v>'11101011'</c:v>
+                  </c:pt>
+                  <c:pt idx="239">
+                    <c:v>'11101101'</c:v>
+                  </c:pt>
+                  <c:pt idx="240">
+                    <c:v>'11101110'</c:v>
+                  </c:pt>
+                  <c:pt idx="241">
+                    <c:v>'11110011'</c:v>
+                  </c:pt>
+                  <c:pt idx="242">
+                    <c:v>'11110101'</c:v>
+                  </c:pt>
+                  <c:pt idx="243">
+                    <c:v>'11110110'</c:v>
+                  </c:pt>
+                  <c:pt idx="244">
+                    <c:v>'11111001'</c:v>
+                  </c:pt>
+                  <c:pt idx="245">
+                    <c:v>'11111010'</c:v>
+                  </c:pt>
+                  <c:pt idx="246">
+                    <c:v>'11111100'</c:v>
+                  </c:pt>
+                  <c:pt idx="247">
+                    <c:v>'01111111'</c:v>
+                  </c:pt>
+                  <c:pt idx="248">
+                    <c:v>'10111111'</c:v>
+                  </c:pt>
+                  <c:pt idx="249">
+                    <c:v>'11011111'</c:v>
+                  </c:pt>
+                  <c:pt idx="250">
+                    <c:v>'11101111'</c:v>
+                  </c:pt>
+                  <c:pt idx="251">
+                    <c:v>'11110111'</c:v>
+                  </c:pt>
+                  <c:pt idx="252">
+                    <c:v>'11111011'</c:v>
+                  </c:pt>
+                  <c:pt idx="253">
+                    <c:v>'11111101'</c:v>
+                  </c:pt>
+                  <c:pt idx="254">
+                    <c:v>'11111110'</c:v>
+                  </c:pt>
+                  <c:pt idx="255">
+                    <c:v>'11111111'</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="31">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="32">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="33">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="34">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="35">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="36">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="37">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="38">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="39">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="40">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="41">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="42">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="43">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="44">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="45">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="46">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="47">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="48">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="49">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="50">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="51">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="52">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="53">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="54">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="55">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="56">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="57">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="58">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="59">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="60">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="61">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="62">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="63">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="64">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="65">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="66">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="67">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="68">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="69">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="70">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="71">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="72">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="73">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="74">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="75">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="76">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="77">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="78">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="79">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="80">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="81">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="82">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="83">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="84">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="85">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="86">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="87">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="88">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="89">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="90">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="91">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="92">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="93">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="94">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="95">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="96">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="97">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="98">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="99">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="100">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="101">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="102">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="103">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="104">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="105">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="106">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="107">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="108">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="109">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="110">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="111">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="112">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="113">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="114">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="115">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="116">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="117">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="118">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="119">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="120">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="121">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="122">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="123">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="124">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="125">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="126">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="127">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="128">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="129">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="130">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="131">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="132">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="133">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="134">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="135">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="136">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="137">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="138">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="139">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="140">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="141">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="142">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="143">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="144">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="145">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="146">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="147">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="148">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="149">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="150">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="151">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="152">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="153">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="154">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="155">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="156">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="157">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="158">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="159">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="160">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="161">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="162">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="163">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="164">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="165">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="166">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="167">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="168">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="169">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="170">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="171">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="172">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="173">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="174">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="175">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="176">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="177">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="178">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="179">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="180">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="181">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="182">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="183">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="184">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="185">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="186">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="187">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="188">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="189">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="190">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="191">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="192">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="193">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="194">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="195">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="196">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="197">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="198">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="199">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="200">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="201">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="202">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="203">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="204">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="205">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="206">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="207">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="208">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="209">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="210">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="211">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="212">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="213">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="214">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="215">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="216">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="217">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="218">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="219">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="220">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="221">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="222">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="223">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="224">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="225">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="226">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="227">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="228">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="229">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="230">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="231">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="232">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="233">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="234">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="235">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="236">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="237">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="238">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="239">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="240">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="241">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="242">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="243">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="244">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="245">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="246">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="247">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="248">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="249">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="250">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="251">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="252">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="253">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="254">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="255">
+                    <c:v>8</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja2!$C$2:$C$257</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="256"/>
+                <c:pt idx="0">
+                  <c:v>285477</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18978</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18897</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18854</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18617</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18354</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18517</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18448</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18685</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4163</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4293</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4285</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4168</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4250</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4210</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4161</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4239</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4223</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4273</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4236</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4142</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4351</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4185</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4281</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4188</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8060</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>7999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7929</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7891</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7842</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8122</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7853</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7856</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>8063</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>8073</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7909</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7843</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2273</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2354</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2224</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2253</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2295</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2336</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2339</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2349</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2319</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2364</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2251</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2360</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2299</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2347</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2316</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2339</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2232</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2381</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2355</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2307</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2350</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2305</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2312</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2265</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2287</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2377</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2295</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2356</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2348</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2356</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2345</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2347</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2306</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2352</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2259</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2349</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2258</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2269</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>2347</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>2301</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2382</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2328</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>2311</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2273</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2350</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2308</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2316</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2368</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>4923</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4631</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4790</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4993</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4822</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4957</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4721</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4673</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>1825</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>1766</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1784</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1808</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1775</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1803</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1845</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1824</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1575</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1635</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>1592</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>1640</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>1604</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>1569</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>1821</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1764</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>1740</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1787</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1639</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1583</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1539</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1619</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1597</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>1628</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>1609</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>1612</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>1642</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>1628</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>1623</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>1603</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>1715</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>1762</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>1796</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>1740</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>1823</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>1829</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>1846</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>1631</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>1619</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>1673</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>1555</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>1664</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>1605</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>1615</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>1572</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>1644</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1680</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>1692</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1658</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>1751</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>1816</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>1832</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>1693</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>1634</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>1598</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>1594</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>1679</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>1515</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>1643</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>1706</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>1763</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>1827</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>1752</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>1770</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>1784</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>1813</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>1840</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>3799</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>3659</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>1598</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>1715</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1447</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1402</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>1395</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1429</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1592</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1435</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1394</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1368</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1358</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1417</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>1402</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1462</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1406</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1340</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1394</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1366</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1392</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1364</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1442</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1716</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1437</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1420</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>1317</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>1471</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>1389</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1456</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>1448</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1419</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1389</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1370</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>1375</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1366</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1465</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1385</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1454</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>1431</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>1369</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>1421</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>1406</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>1334</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>1426</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>1337</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>1445</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>1373</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>1399</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>1442</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>1356</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>1350</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>1410</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>1364</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>1616</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>1596</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>1662</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>1626</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>1316</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>1394</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>1397</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>1235</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>1346</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>1280</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>1302</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>1359</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>1354</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>1315</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>1313</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>1230</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>1313</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>1410</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>1239</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>1304</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>1293</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>1310</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>1330</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>1312</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>1286</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>1288</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>1341</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>1285</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>1318</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>1367</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>1411</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>1391</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>1357</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>1283</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>1362</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>1382</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>1274</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>1302</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>1238</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>1289</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>1441</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-74BA-4934-9368-AE4F02A83594}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="429863704"/>
+        <c:axId val="429859768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="356841632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="356845896"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="356845896"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="356841632"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="429859768"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:min val="1000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="429863704"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="429863704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="429859768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5923,6 +11015,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6478,6 +11610,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -6513,8 +12161,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>695325</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="genotype_histogram" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="genotype_histogram" connectionId="2" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10394,4 +16081,3622 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D257"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>285477</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>18978</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>18897</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>18854</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>18617</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>18354</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8">
+        <v>18517</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9">
+        <v>18448</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10">
+        <v>18685</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11">
+        <v>4163</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12">
+        <v>4293</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13">
+        <v>4285</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>4168</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15">
+        <v>4250</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16">
+        <v>4210</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17">
+        <v>4161</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18">
+        <v>4239</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19">
+        <v>4223</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20">
+        <v>4273</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21">
+        <v>4236</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22">
+        <v>4142</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23">
+        <v>4351</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24">
+        <v>4185</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25">
+        <v>4281</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C26">
+        <v>4188</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>8060</v>
+      </c>
+      <c r="D27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28">
+        <v>7999</v>
+      </c>
+      <c r="D28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29">
+        <v>7929</v>
+      </c>
+      <c r="D29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30">
+        <v>7891</v>
+      </c>
+      <c r="D30">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31">
+        <v>7842</v>
+      </c>
+      <c r="D31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32">
+        <v>8122</v>
+      </c>
+      <c r="D32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33">
+        <v>7853</v>
+      </c>
+      <c r="D33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34">
+        <v>7856</v>
+      </c>
+      <c r="D34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2</v>
+      </c>
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35">
+        <v>8063</v>
+      </c>
+      <c r="D35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2</v>
+      </c>
+      <c r="B36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36">
+        <v>8073</v>
+      </c>
+      <c r="D36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2</v>
+      </c>
+      <c r="B37" t="s">
+        <v>164</v>
+      </c>
+      <c r="C37">
+        <v>7909</v>
+      </c>
+      <c r="D37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2</v>
+      </c>
+      <c r="B38" t="s">
+        <v>196</v>
+      </c>
+      <c r="C38">
+        <v>7843</v>
+      </c>
+      <c r="D38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39">
+        <v>2273</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40">
+        <v>2354</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41">
+        <v>2224</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42">
+        <v>2253</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43">
+        <v>2295</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44">
+        <v>2336</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45">
+        <v>2339</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46">
+        <v>2349</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47">
+        <v>2319</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>3</v>
+      </c>
+      <c r="B48" t="s">
+        <v>45</v>
+      </c>
+      <c r="C48">
+        <v>2364</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>3</v>
+      </c>
+      <c r="B49" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49">
+        <v>2251</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s">
+        <v>48</v>
+      </c>
+      <c r="C50">
+        <v>2360</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51">
+        <v>2299</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>3</v>
+      </c>
+      <c r="B52" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52">
+        <v>2347</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53">
+        <v>2316</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54">
+        <v>2339</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>3</v>
+      </c>
+      <c r="B55" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55">
+        <v>2232</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56">
+        <v>2381</v>
+      </c>
+      <c r="D56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s">
+        <v>74</v>
+      </c>
+      <c r="C57">
+        <v>2355</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s">
+        <v>77</v>
+      </c>
+      <c r="C58">
+        <v>2307</v>
+      </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>3</v>
+      </c>
+      <c r="B59" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59">
+        <v>2350</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s">
+        <v>80</v>
+      </c>
+      <c r="C60">
+        <v>2305</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>3</v>
+      </c>
+      <c r="B61" t="s">
+        <v>85</v>
+      </c>
+      <c r="C61">
+        <v>2312</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62">
+        <v>2265</v>
+      </c>
+      <c r="D62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63">
+        <v>2287</v>
+      </c>
+      <c r="D63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s">
+        <v>92</v>
+      </c>
+      <c r="C64">
+        <v>2377</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>101</v>
+      </c>
+      <c r="C65">
+        <v>2295</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66">
+        <v>2356</v>
+      </c>
+      <c r="D66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>104</v>
+      </c>
+      <c r="C67">
+        <v>2348</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>3</v>
+      </c>
+      <c r="B68" t="s">
+        <v>108</v>
+      </c>
+      <c r="C68">
+        <v>2356</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>3</v>
+      </c>
+      <c r="B69" t="s">
+        <v>135</v>
+      </c>
+      <c r="C69">
+        <v>2345</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>3</v>
+      </c>
+      <c r="B70" t="s">
+        <v>137</v>
+      </c>
+      <c r="C70">
+        <v>2347</v>
+      </c>
+      <c r="D70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>3</v>
+      </c>
+      <c r="B71" t="s">
+        <v>138</v>
+      </c>
+      <c r="C71">
+        <v>2306</v>
+      </c>
+      <c r="D71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>3</v>
+      </c>
+      <c r="B72" t="s">
+        <v>141</v>
+      </c>
+      <c r="C72">
+        <v>2352</v>
+      </c>
+      <c r="D72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>3</v>
+      </c>
+      <c r="B73" t="s">
+        <v>142</v>
+      </c>
+      <c r="C73">
+        <v>2259</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>3</v>
+      </c>
+      <c r="B74" t="s">
+        <v>144</v>
+      </c>
+      <c r="C74">
+        <v>2349</v>
+      </c>
+      <c r="D74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>3</v>
+      </c>
+      <c r="B75" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75">
+        <v>2258</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>3</v>
+      </c>
+      <c r="B76" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76">
+        <v>2269</v>
+      </c>
+      <c r="D76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>3</v>
+      </c>
+      <c r="B77" t="s">
+        <v>152</v>
+      </c>
+      <c r="C77">
+        <v>2347</v>
+      </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>3</v>
+      </c>
+      <c r="B78" t="s">
+        <v>156</v>
+      </c>
+      <c r="C78">
+        <v>2301</v>
+      </c>
+      <c r="D78">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>3</v>
+      </c>
+      <c r="B79" t="s">
+        <v>165</v>
+      </c>
+      <c r="C79">
+        <v>2382</v>
+      </c>
+      <c r="D79">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>3</v>
+      </c>
+      <c r="B80" t="s">
+        <v>166</v>
+      </c>
+      <c r="C80">
+        <v>2328</v>
+      </c>
+      <c r="D80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>3</v>
+      </c>
+      <c r="B81" t="s">
+        <v>168</v>
+      </c>
+      <c r="C81">
+        <v>2311</v>
+      </c>
+      <c r="D81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>3</v>
+      </c>
+      <c r="B82" t="s">
+        <v>172</v>
+      </c>
+      <c r="C82">
+        <v>2273</v>
+      </c>
+      <c r="D82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>3</v>
+      </c>
+      <c r="B83" t="s">
+        <v>197</v>
+      </c>
+      <c r="C83">
+        <v>2350</v>
+      </c>
+      <c r="D83">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>3</v>
+      </c>
+      <c r="B84" t="s">
+        <v>198</v>
+      </c>
+      <c r="C84">
+        <v>2308</v>
+      </c>
+      <c r="D84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>3</v>
+      </c>
+      <c r="B85" t="s">
+        <v>200</v>
+      </c>
+      <c r="C85">
+        <v>2316</v>
+      </c>
+      <c r="D85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>3</v>
+      </c>
+      <c r="B86" t="s">
+        <v>204</v>
+      </c>
+      <c r="C86">
+        <v>2368</v>
+      </c>
+      <c r="D86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>3</v>
+      </c>
+      <c r="B87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87">
+        <v>4923</v>
+      </c>
+      <c r="D87">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>3</v>
+      </c>
+      <c r="B88" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88">
+        <v>4631</v>
+      </c>
+      <c r="D88">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>3</v>
+      </c>
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89">
+        <v>4790</v>
+      </c>
+      <c r="D89">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>3</v>
+      </c>
+      <c r="B90" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90">
+        <v>4993</v>
+      </c>
+      <c r="D90">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>3</v>
+      </c>
+      <c r="B91" t="s">
+        <v>116</v>
+      </c>
+      <c r="C91">
+        <v>4822</v>
+      </c>
+      <c r="D91">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>3</v>
+      </c>
+      <c r="B92" t="s">
+        <v>180</v>
+      </c>
+      <c r="C92">
+        <v>4957</v>
+      </c>
+      <c r="D92">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>3</v>
+      </c>
+      <c r="B93" t="s">
+        <v>212</v>
+      </c>
+      <c r="C93">
+        <v>4721</v>
+      </c>
+      <c r="D93">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>3</v>
+      </c>
+      <c r="B94" t="s">
+        <v>228</v>
+      </c>
+      <c r="C94">
+        <v>4673</v>
+      </c>
+      <c r="D94">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>4</v>
+      </c>
+      <c r="B95" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95">
+        <v>1825</v>
+      </c>
+      <c r="D95">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>4</v>
+      </c>
+      <c r="B96" t="s">
+        <v>31</v>
+      </c>
+      <c r="C96">
+        <v>1766</v>
+      </c>
+      <c r="D96">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>4</v>
+      </c>
+      <c r="B97" t="s">
+        <v>33</v>
+      </c>
+      <c r="C97">
+        <v>1784</v>
+      </c>
+      <c r="D97">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>4</v>
+      </c>
+      <c r="B98" t="s">
+        <v>34</v>
+      </c>
+      <c r="C98">
+        <v>1808</v>
+      </c>
+      <c r="D98">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>4</v>
+      </c>
+      <c r="B99" t="s">
+        <v>43</v>
+      </c>
+      <c r="C99">
+        <v>1775</v>
+      </c>
+      <c r="D99">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>4</v>
+      </c>
+      <c r="B100" t="s">
+        <v>47</v>
+      </c>
+      <c r="C100">
+        <v>1803</v>
+      </c>
+      <c r="D100">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>4</v>
+      </c>
+      <c r="B101" t="s">
+        <v>49</v>
+      </c>
+      <c r="C101">
+        <v>1845</v>
+      </c>
+      <c r="D101">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>4</v>
+      </c>
+      <c r="B102" t="s">
+        <v>50</v>
+      </c>
+      <c r="C102">
+        <v>1824</v>
+      </c>
+      <c r="D102">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>4</v>
+      </c>
+      <c r="B103" t="s">
+        <v>55</v>
+      </c>
+      <c r="C103">
+        <v>1575</v>
+      </c>
+      <c r="D103">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>4</v>
+      </c>
+      <c r="B104" t="s">
+        <v>57</v>
+      </c>
+      <c r="C104">
+        <v>1635</v>
+      </c>
+      <c r="D104">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>4</v>
+      </c>
+      <c r="B105" t="s">
+        <v>58</v>
+      </c>
+      <c r="C105">
+        <v>1592</v>
+      </c>
+      <c r="D105">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>4</v>
+      </c>
+      <c r="B106" t="s">
+        <v>61</v>
+      </c>
+      <c r="C106">
+        <v>1640</v>
+      </c>
+      <c r="D106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>4</v>
+      </c>
+      <c r="B107" t="s">
+        <v>62</v>
+      </c>
+      <c r="C107">
+        <v>1604</v>
+      </c>
+      <c r="D107">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>4</v>
+      </c>
+      <c r="B108" t="s">
+        <v>64</v>
+      </c>
+      <c r="C108">
+        <v>1569</v>
+      </c>
+      <c r="D108">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>4</v>
+      </c>
+      <c r="B109" t="s">
+        <v>75</v>
+      </c>
+      <c r="C109">
+        <v>1821</v>
+      </c>
+      <c r="D109">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>4</v>
+      </c>
+      <c r="B110" t="s">
+        <v>79</v>
+      </c>
+      <c r="C110">
+        <v>1764</v>
+      </c>
+      <c r="D110">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>4</v>
+      </c>
+      <c r="B111" t="s">
+        <v>81</v>
+      </c>
+      <c r="C111">
+        <v>1740</v>
+      </c>
+      <c r="D111">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>4</v>
+      </c>
+      <c r="B112" t="s">
+        <v>82</v>
+      </c>
+      <c r="C112">
+        <v>1787</v>
+      </c>
+      <c r="D112">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>4</v>
+      </c>
+      <c r="B113" t="s">
+        <v>87</v>
+      </c>
+      <c r="C113">
+        <v>1639</v>
+      </c>
+      <c r="D113">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>4</v>
+      </c>
+      <c r="B114" t="s">
+        <v>89</v>
+      </c>
+      <c r="C114">
+        <v>1583</v>
+      </c>
+      <c r="D114">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>4</v>
+      </c>
+      <c r="B115" t="s">
+        <v>90</v>
+      </c>
+      <c r="C115">
+        <v>1539</v>
+      </c>
+      <c r="D115">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>4</v>
+      </c>
+      <c r="B116" t="s">
+        <v>93</v>
+      </c>
+      <c r="C116">
+        <v>1619</v>
+      </c>
+      <c r="D116">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>4</v>
+      </c>
+      <c r="B117" t="s">
+        <v>94</v>
+      </c>
+      <c r="C117">
+        <v>1597</v>
+      </c>
+      <c r="D117">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>4</v>
+      </c>
+      <c r="B118" t="s">
+        <v>96</v>
+      </c>
+      <c r="C118">
+        <v>1628</v>
+      </c>
+      <c r="D118">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>4</v>
+      </c>
+      <c r="B119" t="s">
+        <v>103</v>
+      </c>
+      <c r="C119">
+        <v>1609</v>
+      </c>
+      <c r="D119">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>4</v>
+      </c>
+      <c r="B120" t="s">
+        <v>105</v>
+      </c>
+      <c r="C120">
+        <v>1612</v>
+      </c>
+      <c r="D120">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>4</v>
+      </c>
+      <c r="B121" t="s">
+        <v>106</v>
+      </c>
+      <c r="C121">
+        <v>1642</v>
+      </c>
+      <c r="D121">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>4</v>
+      </c>
+      <c r="B122" t="s">
+        <v>109</v>
+      </c>
+      <c r="C122">
+        <v>1628</v>
+      </c>
+      <c r="D122">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>4</v>
+      </c>
+      <c r="B123" t="s">
+        <v>110</v>
+      </c>
+      <c r="C123">
+        <v>1623</v>
+      </c>
+      <c r="D123">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>4</v>
+      </c>
+      <c r="B124" t="s">
+        <v>112</v>
+      </c>
+      <c r="C124">
+        <v>1603</v>
+      </c>
+      <c r="D124">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>4</v>
+      </c>
+      <c r="B125" t="s">
+        <v>117</v>
+      </c>
+      <c r="C125">
+        <v>1715</v>
+      </c>
+      <c r="D125">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>4</v>
+      </c>
+      <c r="B126" t="s">
+        <v>118</v>
+      </c>
+      <c r="C126">
+        <v>1881</v>
+      </c>
+      <c r="D126">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>4</v>
+      </c>
+      <c r="B127" t="s">
+        <v>120</v>
+      </c>
+      <c r="C127">
+        <v>1762</v>
+      </c>
+      <c r="D127">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>4</v>
+      </c>
+      <c r="B128" t="s">
+        <v>124</v>
+      </c>
+      <c r="C128">
+        <v>1796</v>
+      </c>
+      <c r="D128">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>4</v>
+      </c>
+      <c r="B129" t="s">
+        <v>139</v>
+      </c>
+      <c r="C129">
+        <v>1740</v>
+      </c>
+      <c r="D129">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>4</v>
+      </c>
+      <c r="B130" t="s">
+        <v>143</v>
+      </c>
+      <c r="C130">
+        <v>1823</v>
+      </c>
+      <c r="D130">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>4</v>
+      </c>
+      <c r="B131" t="s">
+        <v>145</v>
+      </c>
+      <c r="C131">
+        <v>1829</v>
+      </c>
+      <c r="D131">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>4</v>
+      </c>
+      <c r="B132" t="s">
+        <v>146</v>
+      </c>
+      <c r="C132">
+        <v>1846</v>
+      </c>
+      <c r="D132">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>4</v>
+      </c>
+      <c r="B133" t="s">
+        <v>151</v>
+      </c>
+      <c r="C133">
+        <v>1631</v>
+      </c>
+      <c r="D133">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>4</v>
+      </c>
+      <c r="B134" t="s">
+        <v>153</v>
+      </c>
+      <c r="C134">
+        <v>1619</v>
+      </c>
+      <c r="D134">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>4</v>
+      </c>
+      <c r="B135" t="s">
+        <v>154</v>
+      </c>
+      <c r="C135">
+        <v>1673</v>
+      </c>
+      <c r="D135">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>4</v>
+      </c>
+      <c r="B136" t="s">
+        <v>157</v>
+      </c>
+      <c r="C136">
+        <v>1555</v>
+      </c>
+      <c r="D136">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>4</v>
+      </c>
+      <c r="B137" t="s">
+        <v>158</v>
+      </c>
+      <c r="C137">
+        <v>1664</v>
+      </c>
+      <c r="D137">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>4</v>
+      </c>
+      <c r="B138" t="s">
+        <v>160</v>
+      </c>
+      <c r="C138">
+        <v>1605</v>
+      </c>
+      <c r="D138">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>4</v>
+      </c>
+      <c r="B139" t="s">
+        <v>167</v>
+      </c>
+      <c r="C139">
+        <v>1615</v>
+      </c>
+      <c r="D139">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>4</v>
+      </c>
+      <c r="B140" t="s">
+        <v>169</v>
+      </c>
+      <c r="C140">
+        <v>1572</v>
+      </c>
+      <c r="D140">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>4</v>
+      </c>
+      <c r="B141" t="s">
+        <v>170</v>
+      </c>
+      <c r="C141">
+        <v>1644</v>
+      </c>
+      <c r="D141">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>4</v>
+      </c>
+      <c r="B142" t="s">
+        <v>173</v>
+      </c>
+      <c r="C142">
+        <v>1680</v>
+      </c>
+      <c r="D142">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>4</v>
+      </c>
+      <c r="B143" t="s">
+        <v>174</v>
+      </c>
+      <c r="C143">
+        <v>1692</v>
+      </c>
+      <c r="D143">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>4</v>
+      </c>
+      <c r="B144" t="s">
+        <v>176</v>
+      </c>
+      <c r="C144">
+        <v>1658</v>
+      </c>
+      <c r="D144">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>4</v>
+      </c>
+      <c r="B145" t="s">
+        <v>181</v>
+      </c>
+      <c r="C145">
+        <v>1751</v>
+      </c>
+      <c r="D145">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>4</v>
+      </c>
+      <c r="B146" t="s">
+        <v>182</v>
+      </c>
+      <c r="C146">
+        <v>1816</v>
+      </c>
+      <c r="D146">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>4</v>
+      </c>
+      <c r="B147" t="s">
+        <v>184</v>
+      </c>
+      <c r="C147">
+        <v>1832</v>
+      </c>
+      <c r="D147">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>4</v>
+      </c>
+      <c r="B148" t="s">
+        <v>188</v>
+      </c>
+      <c r="C148">
+        <v>1693</v>
+      </c>
+      <c r="D148">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>4</v>
+      </c>
+      <c r="B149" t="s">
+        <v>199</v>
+      </c>
+      <c r="C149">
+        <v>1634</v>
+      </c>
+      <c r="D149">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>4</v>
+      </c>
+      <c r="B150" t="s">
+        <v>201</v>
+      </c>
+      <c r="C150">
+        <v>1598</v>
+      </c>
+      <c r="D150">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>4</v>
+      </c>
+      <c r="B151" t="s">
+        <v>202</v>
+      </c>
+      <c r="C151">
+        <v>1594</v>
+      </c>
+      <c r="D151">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>4</v>
+      </c>
+      <c r="B152" t="s">
+        <v>205</v>
+      </c>
+      <c r="C152">
+        <v>1679</v>
+      </c>
+      <c r="D152">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>4</v>
+      </c>
+      <c r="B153" t="s">
+        <v>206</v>
+      </c>
+      <c r="C153">
+        <v>1515</v>
+      </c>
+      <c r="D153">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>4</v>
+      </c>
+      <c r="B154" t="s">
+        <v>208</v>
+      </c>
+      <c r="C154">
+        <v>1643</v>
+      </c>
+      <c r="D154">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>4</v>
+      </c>
+      <c r="B155" t="s">
+        <v>213</v>
+      </c>
+      <c r="C155">
+        <v>1706</v>
+      </c>
+      <c r="D155">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>4</v>
+      </c>
+      <c r="B156" t="s">
+        <v>214</v>
+      </c>
+      <c r="C156">
+        <v>1763</v>
+      </c>
+      <c r="D156">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>4</v>
+      </c>
+      <c r="B157" t="s">
+        <v>216</v>
+      </c>
+      <c r="C157">
+        <v>1827</v>
+      </c>
+      <c r="D157">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>4</v>
+      </c>
+      <c r="B158" t="s">
+        <v>220</v>
+      </c>
+      <c r="C158">
+        <v>1752</v>
+      </c>
+      <c r="D158">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>4</v>
+      </c>
+      <c r="B159" t="s">
+        <v>229</v>
+      </c>
+      <c r="C159">
+        <v>1770</v>
+      </c>
+      <c r="D159">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>4</v>
+      </c>
+      <c r="B160" t="s">
+        <v>230</v>
+      </c>
+      <c r="C160">
+        <v>1784</v>
+      </c>
+      <c r="D160">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>4</v>
+      </c>
+      <c r="B161" t="s">
+        <v>232</v>
+      </c>
+      <c r="C161">
+        <v>1813</v>
+      </c>
+      <c r="D161">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>4</v>
+      </c>
+      <c r="B162" t="s">
+        <v>236</v>
+      </c>
+      <c r="C162">
+        <v>1840</v>
+      </c>
+      <c r="D162">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>4</v>
+      </c>
+      <c r="B163" t="s">
+        <v>19</v>
+      </c>
+      <c r="C163">
+        <v>3799</v>
+      </c>
+      <c r="D163">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>4</v>
+      </c>
+      <c r="B164" t="s">
+        <v>244</v>
+      </c>
+      <c r="C164">
+        <v>3659</v>
+      </c>
+      <c r="D164">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>5</v>
+      </c>
+      <c r="B165" t="s">
+        <v>35</v>
+      </c>
+      <c r="C165">
+        <v>1598</v>
+      </c>
+      <c r="D165">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>5</v>
+      </c>
+      <c r="B166" t="s">
+        <v>51</v>
+      </c>
+      <c r="C166">
+        <v>1715</v>
+      </c>
+      <c r="D166">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>5</v>
+      </c>
+      <c r="B167" t="s">
+        <v>59</v>
+      </c>
+      <c r="C167">
+        <v>1447</v>
+      </c>
+      <c r="D167">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>5</v>
+      </c>
+      <c r="B168" t="s">
+        <v>63</v>
+      </c>
+      <c r="C168">
+        <v>1402</v>
+      </c>
+      <c r="D168">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>5</v>
+      </c>
+      <c r="B169" t="s">
+        <v>65</v>
+      </c>
+      <c r="C169">
+        <v>1395</v>
+      </c>
+      <c r="D169">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>5</v>
+      </c>
+      <c r="B170" t="s">
+        <v>66</v>
+      </c>
+      <c r="C170">
+        <v>1429</v>
+      </c>
+      <c r="D170">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>5</v>
+      </c>
+      <c r="B171" t="s">
+        <v>83</v>
+      </c>
+      <c r="C171">
+        <v>1592</v>
+      </c>
+      <c r="D171">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>5</v>
+      </c>
+      <c r="B172" t="s">
+        <v>91</v>
+      </c>
+      <c r="C172">
+        <v>1435</v>
+      </c>
+      <c r="D172">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>5</v>
+      </c>
+      <c r="B173" t="s">
+        <v>95</v>
+      </c>
+      <c r="C173">
+        <v>1394</v>
+      </c>
+      <c r="D173">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>5</v>
+      </c>
+      <c r="B174" t="s">
+        <v>97</v>
+      </c>
+      <c r="C174">
+        <v>1368</v>
+      </c>
+      <c r="D174">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>5</v>
+      </c>
+      <c r="B175" t="s">
+        <v>98</v>
+      </c>
+      <c r="C175">
+        <v>1358</v>
+      </c>
+      <c r="D175">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>5</v>
+      </c>
+      <c r="B176" t="s">
+        <v>107</v>
+      </c>
+      <c r="C176">
+        <v>1417</v>
+      </c>
+      <c r="D176">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>5</v>
+      </c>
+      <c r="B177" t="s">
+        <v>111</v>
+      </c>
+      <c r="C177">
+        <v>1402</v>
+      </c>
+      <c r="D177">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>5</v>
+      </c>
+      <c r="B178" t="s">
+        <v>113</v>
+      </c>
+      <c r="C178">
+        <v>1462</v>
+      </c>
+      <c r="D178">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>5</v>
+      </c>
+      <c r="B179" t="s">
+        <v>114</v>
+      </c>
+      <c r="C179">
+        <v>1406</v>
+      </c>
+      <c r="D179">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>5</v>
+      </c>
+      <c r="B180" t="s">
+        <v>119</v>
+      </c>
+      <c r="C180">
+        <v>1340</v>
+      </c>
+      <c r="D180">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>5</v>
+      </c>
+      <c r="B181" t="s">
+        <v>121</v>
+      </c>
+      <c r="C181">
+        <v>1394</v>
+      </c>
+      <c r="D181">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>5</v>
+      </c>
+      <c r="B182" t="s">
+        <v>122</v>
+      </c>
+      <c r="C182">
+        <v>1366</v>
+      </c>
+      <c r="D182">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>5</v>
+      </c>
+      <c r="B183" t="s">
+        <v>125</v>
+      </c>
+      <c r="C183">
+        <v>1392</v>
+      </c>
+      <c r="D183">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>5</v>
+      </c>
+      <c r="B184" t="s">
+        <v>126</v>
+      </c>
+      <c r="C184">
+        <v>1364</v>
+      </c>
+      <c r="D184">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>5</v>
+      </c>
+      <c r="B185" t="s">
+        <v>128</v>
+      </c>
+      <c r="C185">
+        <v>1442</v>
+      </c>
+      <c r="D185">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>5</v>
+      </c>
+      <c r="B186" t="s">
+        <v>147</v>
+      </c>
+      <c r="C186">
+        <v>1716</v>
+      </c>
+      <c r="D186">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>5</v>
+      </c>
+      <c r="B187" t="s">
+        <v>155</v>
+      </c>
+      <c r="C187">
+        <v>1437</v>
+      </c>
+      <c r="D187">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>5</v>
+      </c>
+      <c r="B188" t="s">
+        <v>159</v>
+      </c>
+      <c r="C188">
+        <v>1420</v>
+      </c>
+      <c r="D188">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>5</v>
+      </c>
+      <c r="B189" t="s">
+        <v>161</v>
+      </c>
+      <c r="C189">
+        <v>1317</v>
+      </c>
+      <c r="D189">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>5</v>
+      </c>
+      <c r="B190" t="s">
+        <v>162</v>
+      </c>
+      <c r="C190">
+        <v>1471</v>
+      </c>
+      <c r="D190">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>5</v>
+      </c>
+      <c r="B191" t="s">
+        <v>171</v>
+      </c>
+      <c r="C191">
+        <v>1389</v>
+      </c>
+      <c r="D191">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>5</v>
+      </c>
+      <c r="B192" t="s">
+        <v>175</v>
+      </c>
+      <c r="C192">
+        <v>1456</v>
+      </c>
+      <c r="D192">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>5</v>
+      </c>
+      <c r="B193" t="s">
+        <v>177</v>
+      </c>
+      <c r="C193">
+        <v>1448</v>
+      </c>
+      <c r="D193">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>5</v>
+      </c>
+      <c r="B194" t="s">
+        <v>178</v>
+      </c>
+      <c r="C194">
+        <v>1419</v>
+      </c>
+      <c r="D194">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>5</v>
+      </c>
+      <c r="B195" t="s">
+        <v>183</v>
+      </c>
+      <c r="C195">
+        <v>1389</v>
+      </c>
+      <c r="D195">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>5</v>
+      </c>
+      <c r="B196" t="s">
+        <v>185</v>
+      </c>
+      <c r="C196">
+        <v>1370</v>
+      </c>
+      <c r="D196">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>5</v>
+      </c>
+      <c r="B197" t="s">
+        <v>186</v>
+      </c>
+      <c r="C197">
+        <v>1375</v>
+      </c>
+      <c r="D197">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>5</v>
+      </c>
+      <c r="B198" t="s">
+        <v>189</v>
+      </c>
+      <c r="C198">
+        <v>1366</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>5</v>
+      </c>
+      <c r="B199" t="s">
+        <v>190</v>
+      </c>
+      <c r="C199">
+        <v>1465</v>
+      </c>
+      <c r="D199">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>5</v>
+      </c>
+      <c r="B200" t="s">
+        <v>192</v>
+      </c>
+      <c r="C200">
+        <v>1385</v>
+      </c>
+      <c r="D200">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>5</v>
+      </c>
+      <c r="B201" t="s">
+        <v>203</v>
+      </c>
+      <c r="C201">
+        <v>1454</v>
+      </c>
+      <c r="D201">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>5</v>
+      </c>
+      <c r="B202" t="s">
+        <v>207</v>
+      </c>
+      <c r="C202">
+        <v>1431</v>
+      </c>
+      <c r="D202">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>5</v>
+      </c>
+      <c r="B203" t="s">
+        <v>209</v>
+      </c>
+      <c r="C203">
+        <v>1369</v>
+      </c>
+      <c r="D203">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>5</v>
+      </c>
+      <c r="B204" t="s">
+        <v>210</v>
+      </c>
+      <c r="C204">
+        <v>1421</v>
+      </c>
+      <c r="D204">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>5</v>
+      </c>
+      <c r="B205" t="s">
+        <v>215</v>
+      </c>
+      <c r="C205">
+        <v>1406</v>
+      </c>
+      <c r="D205">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>5</v>
+      </c>
+      <c r="B206" t="s">
+        <v>217</v>
+      </c>
+      <c r="C206">
+        <v>1334</v>
+      </c>
+      <c r="D206">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>5</v>
+      </c>
+      <c r="B207" t="s">
+        <v>218</v>
+      </c>
+      <c r="C207">
+        <v>1426</v>
+      </c>
+      <c r="D207">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>5</v>
+      </c>
+      <c r="B208" t="s">
+        <v>221</v>
+      </c>
+      <c r="C208">
+        <v>1337</v>
+      </c>
+      <c r="D208">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>5</v>
+      </c>
+      <c r="B209" t="s">
+        <v>222</v>
+      </c>
+      <c r="C209">
+        <v>1445</v>
+      </c>
+      <c r="D209">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>5</v>
+      </c>
+      <c r="B210" t="s">
+        <v>224</v>
+      </c>
+      <c r="C210">
+        <v>1373</v>
+      </c>
+      <c r="D210">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>5</v>
+      </c>
+      <c r="B211" t="s">
+        <v>231</v>
+      </c>
+      <c r="C211">
+        <v>1399</v>
+      </c>
+      <c r="D211">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>5</v>
+      </c>
+      <c r="B212" t="s">
+        <v>233</v>
+      </c>
+      <c r="C212">
+        <v>1442</v>
+      </c>
+      <c r="D212">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>5</v>
+      </c>
+      <c r="B213" t="s">
+        <v>234</v>
+      </c>
+      <c r="C213">
+        <v>1356</v>
+      </c>
+      <c r="D213">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>5</v>
+      </c>
+      <c r="B214" t="s">
+        <v>237</v>
+      </c>
+      <c r="C214">
+        <v>1350</v>
+      </c>
+      <c r="D214">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>5</v>
+      </c>
+      <c r="B215" t="s">
+        <v>238</v>
+      </c>
+      <c r="C215">
+        <v>1410</v>
+      </c>
+      <c r="D215">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>5</v>
+      </c>
+      <c r="B216" t="s">
+        <v>240</v>
+      </c>
+      <c r="C216">
+        <v>1364</v>
+      </c>
+      <c r="D216">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>5</v>
+      </c>
+      <c r="B217" t="s">
+        <v>245</v>
+      </c>
+      <c r="C217">
+        <v>1616</v>
+      </c>
+      <c r="D217">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>5</v>
+      </c>
+      <c r="B218" t="s">
+        <v>246</v>
+      </c>
+      <c r="C218">
+        <v>1596</v>
+      </c>
+      <c r="D218">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>5</v>
+      </c>
+      <c r="B219" t="s">
+        <v>248</v>
+      </c>
+      <c r="C219">
+        <v>1662</v>
+      </c>
+      <c r="D219">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>5</v>
+      </c>
+      <c r="B220" t="s">
+        <v>252</v>
+      </c>
+      <c r="C220">
+        <v>1626</v>
+      </c>
+      <c r="D220">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>6</v>
+      </c>
+      <c r="B221" t="s">
+        <v>67</v>
+      </c>
+      <c r="C221">
+        <v>1316</v>
+      </c>
+      <c r="D221">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>6</v>
+      </c>
+      <c r="B222" t="s">
+        <v>99</v>
+      </c>
+      <c r="C222">
+        <v>1394</v>
+      </c>
+      <c r="D222">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>6</v>
+      </c>
+      <c r="B223" t="s">
+        <v>115</v>
+      </c>
+      <c r="C223">
+        <v>1397</v>
+      </c>
+      <c r="D223">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>6</v>
+      </c>
+      <c r="B224" t="s">
+        <v>123</v>
+      </c>
+      <c r="C224">
+        <v>1235</v>
+      </c>
+      <c r="D224">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>6</v>
+      </c>
+      <c r="B225" t="s">
+        <v>127</v>
+      </c>
+      <c r="C225">
+        <v>1346</v>
+      </c>
+      <c r="D225">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>6</v>
+      </c>
+      <c r="B226" t="s">
+        <v>129</v>
+      </c>
+      <c r="C226">
+        <v>1280</v>
+      </c>
+      <c r="D226">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>6</v>
+      </c>
+      <c r="B227" t="s">
+        <v>130</v>
+      </c>
+      <c r="C227">
+        <v>1302</v>
+      </c>
+      <c r="D227">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>6</v>
+      </c>
+      <c r="B228" t="s">
+        <v>163</v>
+      </c>
+      <c r="C228">
+        <v>1359</v>
+      </c>
+      <c r="D228">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>6</v>
+      </c>
+      <c r="B229" t="s">
+        <v>179</v>
+      </c>
+      <c r="C229">
+        <v>1354</v>
+      </c>
+      <c r="D229">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>6</v>
+      </c>
+      <c r="B230" t="s">
+        <v>187</v>
+      </c>
+      <c r="C230">
+        <v>1315</v>
+      </c>
+      <c r="D230">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>6</v>
+      </c>
+      <c r="B231" t="s">
+        <v>191</v>
+      </c>
+      <c r="C231">
+        <v>1313</v>
+      </c>
+      <c r="D231">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>6</v>
+      </c>
+      <c r="B232" t="s">
+        <v>193</v>
+      </c>
+      <c r="C232">
+        <v>1230</v>
+      </c>
+      <c r="D232">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>6</v>
+      </c>
+      <c r="B233" t="s">
+        <v>194</v>
+      </c>
+      <c r="C233">
+        <v>1313</v>
+      </c>
+      <c r="D233">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>6</v>
+      </c>
+      <c r="B234" t="s">
+        <v>211</v>
+      </c>
+      <c r="C234">
+        <v>1410</v>
+      </c>
+      <c r="D234">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>6</v>
+      </c>
+      <c r="B235" t="s">
+        <v>219</v>
+      </c>
+      <c r="C235">
+        <v>1239</v>
+      </c>
+      <c r="D235">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>6</v>
+      </c>
+      <c r="B236" t="s">
+        <v>223</v>
+      </c>
+      <c r="C236">
+        <v>1304</v>
+      </c>
+      <c r="D236">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>6</v>
+      </c>
+      <c r="B237" t="s">
+        <v>225</v>
+      </c>
+      <c r="C237">
+        <v>1293</v>
+      </c>
+      <c r="D237">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>6</v>
+      </c>
+      <c r="B238" t="s">
+        <v>226</v>
+      </c>
+      <c r="C238">
+        <v>1310</v>
+      </c>
+      <c r="D238">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>6</v>
+      </c>
+      <c r="B239" t="s">
+        <v>235</v>
+      </c>
+      <c r="C239">
+        <v>1330</v>
+      </c>
+      <c r="D239">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>6</v>
+      </c>
+      <c r="B240" t="s">
+        <v>239</v>
+      </c>
+      <c r="C240">
+        <v>1312</v>
+      </c>
+      <c r="D240">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>6</v>
+      </c>
+      <c r="B241" t="s">
+        <v>241</v>
+      </c>
+      <c r="C241">
+        <v>1286</v>
+      </c>
+      <c r="D241">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>6</v>
+      </c>
+      <c r="B242" t="s">
+        <v>242</v>
+      </c>
+      <c r="C242">
+        <v>1288</v>
+      </c>
+      <c r="D242">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>6</v>
+      </c>
+      <c r="B243" t="s">
+        <v>247</v>
+      </c>
+      <c r="C243">
+        <v>1341</v>
+      </c>
+      <c r="D243">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>6</v>
+      </c>
+      <c r="B244" t="s">
+        <v>249</v>
+      </c>
+      <c r="C244">
+        <v>1285</v>
+      </c>
+      <c r="D244">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>6</v>
+      </c>
+      <c r="B245" t="s">
+        <v>250</v>
+      </c>
+      <c r="C245">
+        <v>1318</v>
+      </c>
+      <c r="D245">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>6</v>
+      </c>
+      <c r="B246" t="s">
+        <v>253</v>
+      </c>
+      <c r="C246">
+        <v>1367</v>
+      </c>
+      <c r="D246">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>6</v>
+      </c>
+      <c r="B247" t="s">
+        <v>254</v>
+      </c>
+      <c r="C247">
+        <v>1411</v>
+      </c>
+      <c r="D247">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>6</v>
+      </c>
+      <c r="B248" t="s">
+        <v>256</v>
+      </c>
+      <c r="C248">
+        <v>1391</v>
+      </c>
+      <c r="D248">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>7</v>
+      </c>
+      <c r="B249" t="s">
+        <v>131</v>
+      </c>
+      <c r="C249">
+        <v>1357</v>
+      </c>
+      <c r="D249">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>7</v>
+      </c>
+      <c r="B250" t="s">
+        <v>195</v>
+      </c>
+      <c r="C250">
+        <v>1283</v>
+      </c>
+      <c r="D250">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>7</v>
+      </c>
+      <c r="B251" t="s">
+        <v>227</v>
+      </c>
+      <c r="C251">
+        <v>1362</v>
+      </c>
+      <c r="D251">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>7</v>
+      </c>
+      <c r="B252" t="s">
+        <v>243</v>
+      </c>
+      <c r="C252">
+        <v>1382</v>
+      </c>
+      <c r="D252">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>7</v>
+      </c>
+      <c r="B253" t="s">
+        <v>251</v>
+      </c>
+      <c r="C253">
+        <v>1274</v>
+      </c>
+      <c r="D253">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>7</v>
+      </c>
+      <c r="B254" t="s">
+        <v>255</v>
+      </c>
+      <c r="C254">
+        <v>1302</v>
+      </c>
+      <c r="D254">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>7</v>
+      </c>
+      <c r="B255" t="s">
+        <v>257</v>
+      </c>
+      <c r="C255">
+        <v>1238</v>
+      </c>
+      <c r="D255">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>7</v>
+      </c>
+      <c r="B256" t="s">
+        <v>258</v>
+      </c>
+      <c r="C256">
+        <v>1289</v>
+      </c>
+      <c r="D256">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>8</v>
+      </c>
+      <c r="B257" t="s">
+        <v>259</v>
+      </c>
+      <c r="C257">
+        <v>1441</v>
+      </c>
+      <c r="D257">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:D257">
+    <sortCondition ref="A4"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>